--- a/kraje_wynik.xlsx
+++ b/kraje_wynik.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G4">
@@ -542,7 +542,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G5">
@@ -580,7 +580,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G6">
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G7">
@@ -656,7 +656,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G8">
@@ -694,7 +694,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G9">
@@ -732,7 +732,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G10">
@@ -770,7 +770,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G11">
@@ -808,7 +808,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G12">
@@ -884,7 +884,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G14">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G18">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G19">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G20">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G21">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G22">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G23">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G24">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G25">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G26">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G27">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G32">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G33">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G34">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G39">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G42">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G43">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G44">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G45">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G46">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G47">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G48">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G49">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G50">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G51">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G52">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G53">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G55">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G56">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G57">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G58">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G60">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G61">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G67">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G68">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G69">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G70">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G71">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G72">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G73">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G74">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G75">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G76">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G77">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G79">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G80">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G81">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G82">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G83">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G84">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G85">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G86">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G87">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G88">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G90">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G91">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G92">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G93">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G94">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G95">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G96">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G97">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G99">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G102">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G103">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G104">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G105">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G106">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G107">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G110">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G111">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G112">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G114">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G115">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G116">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G117">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G118">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G123">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G126">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G127">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G128">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G130">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G131">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G132">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G134">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G135">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G136">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G137">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G138">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G139">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G140">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G141">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G142">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G143">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G144">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G145">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G147">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G150">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G151">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G153">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G154">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G156">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G158">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G159">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G160">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G161">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G166">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G167">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G168">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G169">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G170">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G171">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G172">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G173">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G174">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G177">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G178">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G180">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Latin America and Caribbean</t>
+          <t>Latin America &amp; Caribbean</t>
         </is>
       </c>
       <c r="G181">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G182">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G183">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>East Asia and Pacific</t>
+          <t>East Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="G184">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Europe and Central Asia</t>
+          <t>Europe &amp; Central Asia</t>
         </is>
       </c>
       <c r="G185">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Middle East and North Africa</t>
+          <t>Middle East &amp; North Africa</t>
         </is>
       </c>
       <c r="G186">
